--- a/core/books/trade_bot_profitability_2_weeks_50_investment_15_trades.xlsx
+++ b/core/books/trade_bot_profitability_2_weeks_50_investment_15_trades.xlsx
@@ -465,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>80.99999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>43.2</v>
+        <v>25.91999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>91.8</v>
+        <v>55.07999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>441.8</v>
+        <v>350.08</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>80.99999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>43.2</v>
+        <v>25.91999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>91.8</v>
+        <v>55.07999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>533.6</v>
+        <v>405.16</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>135</v>
+        <v>80.99999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>43.2</v>
+        <v>25.91999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>91.8</v>
+        <v>55.07999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>625.4</v>
+        <v>460.24</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>135</v>
+        <v>80.99999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>43.2</v>
+        <v>25.91999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>91.8</v>
+        <v>55.07999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>717.1999999999999</v>
+        <v>515.3199999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>135</v>
+        <v>80.99999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>43.2</v>
+        <v>25.91999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>91.8</v>
+        <v>55.07999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>808.9999999999999</v>
+        <v>570.4</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>80.99999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>43.2</v>
+        <v>25.91999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>91.8</v>
+        <v>55.07999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>900.7999999999998</v>
+        <v>625.48</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +585,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D8" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1010.96</v>
+        <v>691.576</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -605,19 +605,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D9" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1121.12</v>
+        <v>757.672</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D10" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1231.28</v>
+        <v>823.768</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D11" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1341.44</v>
+        <v>889.864</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -665,19 +665,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D12" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1451.6</v>
+        <v>955.96</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -685,19 +685,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D13" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1561.76</v>
+        <v>1022.056</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -705,19 +705,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>162</v>
+        <v>97.19999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>51.83999999999999</v>
+        <v>31.104</v>
       </c>
       <c r="D14" t="n">
-        <v>110.16</v>
+        <v>66.09599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1671.92</v>
+        <v>1088.152</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -725,19 +725,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C15" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D15" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E15" t="n">
-        <v>1804.112</v>
+        <v>1167.4672</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="16">
@@ -745,19 +745,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C16" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D16" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E16" t="n">
-        <v>1936.304</v>
+        <v>1246.7824</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="17">
@@ -765,19 +765,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C17" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D17" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E17" t="n">
-        <v>2068.496</v>
+        <v>1326.0976</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="18">
@@ -785,19 +785,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C18" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D18" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E18" t="n">
-        <v>2200.688</v>
+        <v>1405.4128</v>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="19">
@@ -805,19 +805,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C19" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D19" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E19" t="n">
-        <v>2332.88</v>
+        <v>1484.728</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="20">
@@ -825,19 +825,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C20" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D20" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E20" t="n">
-        <v>2465.072</v>
+        <v>1564.0432</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +845,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>194.4</v>
+        <v>116.64</v>
       </c>
       <c r="C21" t="n">
-        <v>62.20799999999999</v>
+        <v>37.3248</v>
       </c>
       <c r="D21" t="n">
-        <v>132.192</v>
+        <v>79.3152</v>
       </c>
       <c r="E21" t="n">
-        <v>2597.264</v>
+        <v>1643.3584</v>
       </c>
       <c r="F21" t="n">
-        <v>72</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22">
@@ -865,19 +865,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C22" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>2755.8944</v>
+        <v>1738.53664</v>
       </c>
       <c r="F22" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="23">
@@ -885,19 +885,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C23" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>2914.5248</v>
+        <v>1833.71488</v>
       </c>
       <c r="F23" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="24">
@@ -905,19 +905,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C24" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>3073.1552</v>
+        <v>1928.89312</v>
       </c>
       <c r="F24" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +925,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C25" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>3231.7856</v>
+        <v>2024.07136</v>
       </c>
       <c r="F25" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="26">
@@ -945,19 +945,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C26" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>3390.416</v>
+        <v>2119.2496</v>
       </c>
       <c r="F26" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27">
@@ -965,19 +965,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C27" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E27" t="n">
-        <v>3549.0464</v>
+        <v>2214.42784</v>
       </c>
       <c r="F27" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="28">
@@ -985,19 +985,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>233.28</v>
+        <v>139.968</v>
       </c>
       <c r="C28" t="n">
-        <v>74.64960000000001</v>
+        <v>44.78976000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>158.6304</v>
+        <v>95.17824000000002</v>
       </c>
       <c r="E28" t="n">
-        <v>3707.6768</v>
+        <v>2309.60608</v>
       </c>
       <c r="F28" t="n">
-        <v>86.40000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="29">
@@ -1005,19 +1005,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C29" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D29" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E29" t="n">
-        <v>3898.03328</v>
+        <v>2423.819968000001</v>
       </c>
       <c r="F29" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1025,19 +1025,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C30" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D30" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E30" t="n">
-        <v>4088.38976</v>
+        <v>2538.033856000001</v>
       </c>
       <c r="F30" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1045,19 +1045,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C31" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D31" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E31" t="n">
-        <v>4278.74624</v>
+        <v>2652.247744000001</v>
       </c>
       <c r="F31" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1065,19 +1065,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C32" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D32" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E32" t="n">
-        <v>4469.102720000001</v>
+        <v>2766.461632000001</v>
       </c>
       <c r="F32" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1085,19 +1085,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C33" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D33" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E33" t="n">
-        <v>4659.459200000001</v>
+        <v>2880.675520000002</v>
       </c>
       <c r="F33" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1105,19 +1105,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C34" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D34" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E34" t="n">
-        <v>4849.815680000002</v>
+        <v>2994.889408000002</v>
       </c>
       <c r="F34" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1125,19 +1125,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>279.936</v>
+        <v>167.9616</v>
       </c>
       <c r="C35" t="n">
-        <v>89.57952000000002</v>
+        <v>53.747712</v>
       </c>
       <c r="D35" t="n">
-        <v>190.35648</v>
+        <v>114.213888</v>
       </c>
       <c r="E35" t="n">
-        <v>5040.172160000002</v>
+        <v>3109.103296000002</v>
       </c>
       <c r="F35" t="n">
-        <v>103.68</v>
+        <v>62.20800000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1145,19 +1145,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C36" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D36" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E36" t="n">
-        <v>5268.599936000002</v>
+        <v>3246.159961600002</v>
       </c>
       <c r="F36" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1165,19 +1165,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C37" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D37" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E37" t="n">
-        <v>5497.027712000003</v>
+        <v>3383.216627200002</v>
       </c>
       <c r="F37" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1185,19 +1185,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C38" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D38" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E38" t="n">
-        <v>5725.455488000003</v>
+        <v>3520.273292800002</v>
       </c>
       <c r="F38" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1205,19 +1205,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C39" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D39" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E39" t="n">
-        <v>5953.883264000004</v>
+        <v>3657.329958400002</v>
       </c>
       <c r="F39" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1225,19 +1225,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C40" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D40" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E40" t="n">
-        <v>6182.311040000004</v>
+        <v>3794.386624000002</v>
       </c>
       <c r="F40" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1245,19 +1245,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C41" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D41" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E41" t="n">
-        <v>6410.738816000005</v>
+        <v>3931.443289600003</v>
       </c>
       <c r="F41" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1265,19 +1265,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>335.9232</v>
+        <v>201.55392</v>
       </c>
       <c r="C42" t="n">
-        <v>107.495424</v>
+        <v>64.4972544</v>
       </c>
       <c r="D42" t="n">
-        <v>228.427776</v>
+        <v>137.0566656</v>
       </c>
       <c r="E42" t="n">
-        <v>6639.166592000005</v>
+        <v>4068.499955200003</v>
       </c>
       <c r="F42" t="n">
-        <v>124.416</v>
+        <v>74.64960000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1285,19 +1285,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C43" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D43" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E43" t="n">
-        <v>6913.279923200005</v>
+        <v>4232.967953920002</v>
       </c>
       <c r="F43" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="44">
@@ -1305,19 +1305,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C44" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D44" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E44" t="n">
-        <v>7187.393254400005</v>
+        <v>4397.435952640002</v>
       </c>
       <c r="F44" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="45">
@@ -1325,19 +1325,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C45" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D45" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E45" t="n">
-        <v>7461.506585600006</v>
+        <v>4561.903951360002</v>
       </c>
       <c r="F45" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="46">
@@ -1345,19 +1345,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C46" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D46" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E46" t="n">
-        <v>7735.619916800006</v>
+        <v>4726.371950080002</v>
       </c>
       <c r="F46" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1365,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C47" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D47" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E47" t="n">
-        <v>8009.733248000006</v>
+        <v>4890.839948800001</v>
       </c>
       <c r="F47" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="48">
@@ -1385,19 +1385,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C48" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D48" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E48" t="n">
-        <v>8283.846579200006</v>
+        <v>5055.307947520001</v>
       </c>
       <c r="F48" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="49">
@@ -1405,19 +1405,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>403.10784</v>
+        <v>241.864704</v>
       </c>
       <c r="C49" t="n">
-        <v>128.9945088</v>
+        <v>77.39670528000001</v>
       </c>
       <c r="D49" t="n">
-        <v>274.1133312</v>
+        <v>164.46799872</v>
       </c>
       <c r="E49" t="n">
-        <v>8557.959910400006</v>
+        <v>5219.775946240001</v>
       </c>
       <c r="F49" t="n">
-        <v>149.2992</v>
+        <v>89.57952</v>
       </c>
     </row>
     <row r="50">
@@ -1425,19 +1425,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C50" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D50" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E50" t="n">
-        <v>8886.895907840006</v>
+        <v>5417.137544704001</v>
       </c>
       <c r="F50" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="51">
@@ -1445,19 +1445,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C51" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D51" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E51" t="n">
-        <v>9215.831905280005</v>
+        <v>5614.499143168001</v>
       </c>
       <c r="F51" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="52">
@@ -1465,19 +1465,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C52" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D52" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E52" t="n">
-        <v>9544.767902720005</v>
+        <v>5811.860741632001</v>
       </c>
       <c r="F52" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="53">
@@ -1485,19 +1485,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C53" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D53" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E53" t="n">
-        <v>9873.703900160004</v>
+        <v>6009.222340096001</v>
       </c>
       <c r="F53" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="54">
@@ -1505,19 +1505,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C54" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D54" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E54" t="n">
-        <v>10202.6398976</v>
+        <v>6206.583938560001</v>
       </c>
       <c r="F54" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="55">
@@ -1525,19 +1525,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C55" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D55" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E55" t="n">
-        <v>10531.57589504</v>
+        <v>6403.945537024001</v>
       </c>
       <c r="F55" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="56">
@@ -1545,19 +1545,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>483.729408</v>
+        <v>290.2376448</v>
       </c>
       <c r="C56" t="n">
-        <v>154.79341056</v>
+        <v>92.876046336</v>
       </c>
       <c r="D56" t="n">
-        <v>328.9359974400001</v>
+        <v>197.361598464</v>
       </c>
       <c r="E56" t="n">
-        <v>10860.51189248</v>
+        <v>6601.307135488001</v>
       </c>
       <c r="F56" t="n">
-        <v>179.15904</v>
+        <v>107.495424</v>
       </c>
     </row>
     <row r="57">
@@ -1565,19 +1565,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>580.4752896</v>
+        <v>348.28517376</v>
       </c>
       <c r="C57" t="n">
-        <v>185.752092672</v>
+        <v>111.4512556032</v>
       </c>
       <c r="D57" t="n">
-        <v>394.723196928</v>
+        <v>236.8339181568</v>
       </c>
       <c r="E57" t="n">
-        <v>11255.235089408</v>
+        <v>6838.141053644801</v>
       </c>
       <c r="F57" t="n">
-        <v>214.990848</v>
+        <v>128.9945088</v>
       </c>
     </row>
   </sheetData>
